--- a/data/dataset/results/ranking_MWP.xlsx
+++ b/data/dataset/results/ranking_MWP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\llm-goal-scope\data\dataset\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5607100B-77AD-464C-BCB2-30ADD8620400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E319AB2-542A-4A0C-9A0C-9D4D307FD6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{D25027FC-FC27-47EF-8BDA-CB9196E400CB}"/>
   </bookViews>
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -183,7 +183,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,30 +617,30 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>0.25164835164835098</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.31481481481481399</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.44775132275132201</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.53939716999418497</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.61033411033411</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.40201465201465197</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.14583333333333301</v>
+      <c r="D3">
+        <v>0.25484351713859899</v>
+      </c>
+      <c r="E3">
+        <v>0.38585858585858501</v>
+      </c>
+      <c r="F3">
+        <v>0.379212204007286</v>
+      </c>
+      <c r="G3">
+        <v>0.62009803921568596</v>
+      </c>
+      <c r="H3">
+        <v>0.664251207729468</v>
+      </c>
+      <c r="I3">
+        <v>0.60101010101010099</v>
+      </c>
+      <c r="J3">
+        <v>0.15656565656565599</v>
       </c>
       <c r="K3" s="2">
         <f>MAX(D3:J3)</f>
-        <v>0.61033411033411</v>
+        <v>0.664251207729468</v>
       </c>
       <c r="N3" t="s">
         <v>3</v>
@@ -651,7 +650,7 @@
       </c>
       <c r="P3" s="1">
         <f>_xlfn.T.TEST(D3:J3,D7:J7,2,1)</f>
-        <v>0.4135198317247728</v>
+        <v>0.56613887792232842</v>
       </c>
       <c r="R3" t="s">
         <v>3</v>
@@ -664,11 +663,11 @@
       </c>
       <c r="U3" s="2">
         <f>AVERAGE(D3:K3)</f>
-        <v>0.4152659831531097</v>
+        <v>0.46576131490685613</v>
       </c>
       <c r="V3" s="2">
         <f>K3</f>
-        <v>0.61033411033411</v>
+        <v>0.664251207729468</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -681,26 +680,26 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2">
-        <v>0.85049683830171596</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4">
         <v>0.88888888888888795</v>
       </c>
-      <c r="F4" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.64176706827309205</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="E4">
         <v>0.88888888888888795</v>
+      </c>
+      <c r="F4">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="G4">
+        <v>0.86111111111111105</v>
+      </c>
+      <c r="H4">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="I4">
+        <v>0.65079365079365004</v>
+      </c>
+      <c r="J4">
+        <v>0.86111111111111105</v>
       </c>
       <c r="K4" s="2">
         <f t="shared" ref="K4:K16" si="0">MAX(D4:J4)</f>
@@ -714,7 +713,7 @@
       </c>
       <c r="P4" s="1">
         <f>_xlfn.T.TEST(D4:J4,D8:J8,2,1)</f>
-        <v>0.37589475587083437</v>
+        <v>0.50205225650527585</v>
       </c>
       <c r="R4" t="s">
         <v>3</v>
@@ -727,13 +726,12 @@
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4:U16" si="1">AVERAGE(D4:K4)</f>
-        <v>0.85269152490721623</v>
+        <v>0.85218253968253888</v>
       </c>
       <c r="V4" s="2">
         <f t="shared" ref="V4:V16" si="2">K4</f>
         <v>0.88888888888888795</v>
       </c>
-      <c r="X4" s="5"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -745,30 +743,30 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.56451612903225801</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.532258064516129</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.56451612903225801</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.532258064516129</v>
+      <c r="D5">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="E5">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="F5">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="G5">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="H5">
+        <v>0.60628618693134795</v>
+      </c>
+      <c r="I5">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="J5">
+        <v>0.59553349875930495</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" si="0"/>
-        <v>0.56451612903225801</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="N5" t="s">
         <v>3</v>
@@ -778,7 +776,7 @@
       </c>
       <c r="P5" s="1">
         <f>_xlfn.T.TEST(D5:J5,D9:J9,2,1)</f>
-        <v>0.88957907191889296</v>
+        <v>5.5323550731285129E-2</v>
       </c>
       <c r="R5" t="s">
         <v>3</v>
@@ -791,13 +789,12 @@
       </c>
       <c r="U5" s="2">
         <f t="shared" si="1"/>
-        <v>0.5504032258064514</v>
+        <v>0.62107113316790707</v>
       </c>
       <c r="V5" s="2">
         <f t="shared" si="2"/>
-        <v>0.56451612903225801</v>
-      </c>
-      <c r="X5" s="5"/>
+        <v>0.62779156327543395</v>
+      </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -809,30 +806,30 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2">
-        <v>0.93268535020237997</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.93693624809750697</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.937398235085805</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.93921254899805395</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.94103105767865403</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.93818995798279103</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.93469363288751905</v>
+      <c r="D6">
+        <v>0.93669025088477198</v>
+      </c>
+      <c r="E6">
+        <v>0.97951929748316902</v>
+      </c>
+      <c r="F6">
+        <v>0.99155089836204302</v>
+      </c>
+      <c r="G6">
+        <v>0.99079733231383504</v>
+      </c>
+      <c r="H6">
+        <v>0.97886931772310704</v>
+      </c>
+      <c r="I6">
+        <v>0.98281862412784504</v>
+      </c>
+      <c r="J6">
+        <v>0.92074623330840799</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="0"/>
-        <v>0.94103105767865403</v>
+        <v>0.99155089836204302</v>
       </c>
       <c r="N6" t="s">
         <v>3</v>
@@ -842,7 +839,7 @@
       </c>
       <c r="P6" s="1">
         <f>_xlfn.T.TEST(D6:J6,D10:J10,2,1)</f>
-        <v>0.92832456705920974</v>
+        <v>0.85781339370629273</v>
       </c>
       <c r="R6" t="s">
         <v>3</v>
@@ -855,13 +852,12 @@
       </c>
       <c r="U6" s="2">
         <f t="shared" si="1"/>
-        <v>0.9376472610764206</v>
+        <v>0.9715678565706527</v>
       </c>
       <c r="V6" s="2">
         <f t="shared" si="2"/>
-        <v>0.94103105767865403</v>
-      </c>
-      <c r="X6" s="5"/>
+        <v>0.99155089836204302</v>
+      </c>
       <c r="AB6" s="2"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -874,30 +870,30 @@
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="2">
-        <v>0.416901408450704</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.51165501165501104</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.48756218905472598</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.43153594771241799</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.391666666666666</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.45571658615136801</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.42274305555555503</v>
+      <c r="D7">
+        <v>0.43497474747474701</v>
+      </c>
+      <c r="E7">
+        <v>0.54836182336182304</v>
+      </c>
+      <c r="F7">
+        <v>0.45320512820512798</v>
+      </c>
+      <c r="G7">
+        <v>0.62009803921568596</v>
+      </c>
+      <c r="H7">
+        <v>0.39951134930643101</v>
+      </c>
+      <c r="I7">
+        <v>0.47202380952380901</v>
+      </c>
+      <c r="J7">
+        <v>0.439604377104377</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="0"/>
-        <v>0.51165501165501104</v>
+        <v>0.62009803921568596</v>
       </c>
       <c r="N7" t="s">
         <v>10</v>
@@ -907,7 +903,7 @@
       </c>
       <c r="P7" s="1">
         <f>_xlfn.T.TEST(D11:J11,D14:J14,2,1)</f>
-        <v>0.71054454046162729</v>
+        <v>0.3839090032521979</v>
       </c>
       <c r="R7" t="s">
         <v>3</v>
@@ -920,13 +916,12 @@
       </c>
       <c r="U7" s="2">
         <f t="shared" si="1"/>
-        <v>0.45367948461268237</v>
+        <v>0.49848466417596082</v>
       </c>
       <c r="V7" s="2">
         <f t="shared" si="2"/>
-        <v>0.51165501165501104</v>
-      </c>
-      <c r="X7" s="5"/>
+        <v>0.62009803921568596</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -938,26 +933,26 @@
       <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.85049683830171596</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.88753387533875305</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="D8">
+        <v>0.86111111111111105</v>
+      </c>
+      <c r="E8">
         <v>0.88888888888888795</v>
       </c>
-      <c r="J8" s="2">
-        <v>0.88617886178861704</v>
+      <c r="F8">
+        <v>0.86111111111111105</v>
+      </c>
+      <c r="G8">
+        <v>0.88723051409618503</v>
+      </c>
+      <c r="H8">
+        <v>0.86111111111111105</v>
+      </c>
+      <c r="I8">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="J8">
+        <v>0.86111111111111105</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="0"/>
@@ -971,7 +966,7 @@
       </c>
       <c r="P8" s="1">
         <f>_xlfn.T.TEST(D12:J12,D15:J15,2,1)</f>
-        <v>0.59387867307281961</v>
+        <v>0.33884631413949745</v>
       </c>
       <c r="R8" t="s">
         <v>3</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="U8" s="2">
         <f t="shared" si="1"/>
-        <v>0.88307362240289011</v>
+        <v>0.87479270315091151</v>
       </c>
       <c r="V8" s="2">
         <f t="shared" si="2"/>
@@ -1001,30 +996,30 @@
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.56451612903225801</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.54838709677419295</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.56451612903225801</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.51209677419354804</v>
+      <c r="D9">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="E9">
+        <v>0.61972704714640103</v>
+      </c>
+      <c r="F9">
+        <v>0.62779156327543395</v>
+      </c>
+      <c r="G9">
+        <v>0.611662531017369</v>
+      </c>
+      <c r="H9">
+        <v>0.59553349875930495</v>
+      </c>
+      <c r="I9">
+        <v>0.62375930521091805</v>
+      </c>
+      <c r="J9">
+        <v>0.56327543424317605</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="0"/>
-        <v>0.56451612903225801</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="N9" t="s">
         <v>10</v>
@@ -1034,7 +1029,7 @@
       </c>
       <c r="P9" s="1">
         <f>_xlfn.T.TEST(D13:J13,D16:J16,2,1)</f>
-        <v>0.28896857561469869</v>
+        <v>0.92384586893736864</v>
       </c>
       <c r="R9" t="s">
         <v>3</v>
@@ -1047,11 +1042,11 @@
       </c>
       <c r="U9" s="2">
         <f t="shared" si="1"/>
-        <v>0.54989919354838679</v>
+        <v>0.61216656327543384</v>
       </c>
       <c r="V9" s="2">
         <f t="shared" si="2"/>
-        <v>0.56451612903225801</v>
+        <v>0.62779156327543395</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
@@ -1064,30 +1059,30 @@
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2">
-        <v>0.93973917514745398</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.93764496357021698</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.93944455915457203</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.936997318893808</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.93419117816160502</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.93158403611311402</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.93922463682158897</v>
+      <c r="D10">
+        <v>0.99481979448093305</v>
+      </c>
+      <c r="E10">
+        <v>0.94266032312419401</v>
+      </c>
+      <c r="F10">
+        <v>0.98886359468137797</v>
+      </c>
+      <c r="G10">
+        <v>0.98835886192977496</v>
+      </c>
+      <c r="H10">
+        <v>0.93328442743446405</v>
+      </c>
+      <c r="I10">
+        <v>0.98655523612953899</v>
+      </c>
+      <c r="J10">
+        <v>0.92969163495900398</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="0"/>
-        <v>0.93973917514745398</v>
+        <v>0.99481979448093305</v>
       </c>
       <c r="R10" t="s">
         <v>3</v>
@@ -1100,11 +1095,11 @@
       </c>
       <c r="U10" s="2">
         <f t="shared" si="1"/>
-        <v>0.93732063037622659</v>
+        <v>0.96988170840252752</v>
       </c>
       <c r="V10" s="2">
         <f t="shared" si="2"/>
-        <v>0.93973917514745398</v>
+        <v>0.99481979448093305</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
@@ -1117,26 +1112,26 @@
       <c r="C11" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="2">
-        <v>0.99572649572649496</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.98611111111111105</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.99572649572649496</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.97530864197530798</v>
+      <c r="D11">
+        <v>0.99862825788751697</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0.97222222222222199</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="0"/>
@@ -1159,7 +1154,7 @@
       </c>
       <c r="U11" s="2">
         <f t="shared" si="1"/>
-        <v>0.99410909306742612</v>
+        <v>0.99635631001371738</v>
       </c>
       <c r="V11" s="2">
         <f t="shared" si="2"/>
@@ -1176,30 +1171,30 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.68926553672316304</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.677966101694915</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0.677966101694915</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.62288135593220295</v>
+      <c r="D12">
+        <v>0.61016949152542299</v>
+      </c>
+      <c r="E12">
+        <v>0.62711864406779605</v>
+      </c>
+      <c r="F12">
+        <v>0.59322033898305004</v>
+      </c>
+      <c r="G12">
+        <v>0.57627118644067798</v>
+      </c>
+      <c r="H12">
+        <v>0.57627118644067798</v>
+      </c>
+      <c r="I12">
+        <v>0.62711864406779605</v>
+      </c>
+      <c r="J12">
+        <v>0.55367231638418002</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="0"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>16</v>
@@ -1209,7 +1204,7 @@
       </c>
       <c r="P12" s="1">
         <f>_xlfn.T.TEST(D4:J4,D11:J11,2,1)</f>
-        <v>6.2032443080274648E-3</v>
+        <v>4.4277351533955171E-3</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -1222,11 +1217,11 @@
       </c>
       <c r="U12" s="2">
         <f t="shared" si="1"/>
-        <v>0.6894420903954801</v>
+        <v>0.59887005649717462</v>
       </c>
       <c r="V12" s="2">
         <f t="shared" si="2"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
@@ -1239,30 +1234,30 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2">
-        <v>0.91333063316442797</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.93055030097717195</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.91151442820615702</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.90245218913699399</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0.92046569313716597</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.91508525064456303</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.92116310943551005</v>
+      <c r="D13">
+        <v>0.93239539171778496</v>
+      </c>
+      <c r="E13">
+        <v>0.93463006505356605</v>
+      </c>
+      <c r="F13">
+        <v>0.93031331017644503</v>
+      </c>
+      <c r="G13">
+        <v>0.941720406904897</v>
+      </c>
+      <c r="H13">
+        <v>0.93263625000406802</v>
+      </c>
+      <c r="I13">
+        <v>0.93774124646253598</v>
+      </c>
+      <c r="J13">
+        <v>0.93677269555523501</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="0"/>
-        <v>0.93055030097717195</v>
+        <v>0.941720406904897</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" t="s">
@@ -1270,7 +1265,7 @@
       </c>
       <c r="P13" s="1">
         <f>_xlfn.T.TEST(D5:J5,D12:J12,2,1)</f>
-        <v>4.1130660214394762E-6</v>
+        <v>1.4766528441383374E-2</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -1283,11 +1278,11 @@
       </c>
       <c r="U13" s="2">
         <f t="shared" si="1"/>
-        <v>0.91813898820989537</v>
+        <v>0.93599122159742865</v>
       </c>
       <c r="V13" s="2">
         <f t="shared" si="2"/>
-        <v>0.93055030097717195</v>
+        <v>0.941720406904897</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
@@ -1300,26 +1295,26 @@
       <c r="C14" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="2">
-        <v>0.97855750487329396</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.99711399711399695</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0.98611111111111105</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0.97855750487329396</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.99711399711399695</v>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0.99862825788751697</v>
+      </c>
+      <c r="F14">
+        <v>0.99862825788751697</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
       </c>
       <c r="K14" s="2">
         <f t="shared" si="0"/>
@@ -1331,7 +1326,7 @@
       </c>
       <c r="P14" s="1">
         <f>_xlfn.T.TEST(D6:J6,D13:J13,2,1)</f>
-        <v>1.199668002473845E-3</v>
+        <v>1.9665012916914415E-2</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -1344,7 +1339,7 @@
       </c>
       <c r="U14" s="2">
         <f t="shared" si="1"/>
-        <v>0.9921817643857116</v>
+        <v>0.99965706447187919</v>
       </c>
       <c r="V14" s="2">
         <f t="shared" si="2"/>
@@ -1361,30 +1356,30 @@
       <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.68852861704740798</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.69491525423728795</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0.69491525423728795</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0.71186440677966101</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.53672316384180696</v>
+      <c r="D15">
+        <v>0.59322033898305004</v>
+      </c>
+      <c r="E15">
+        <v>0.62711864406779605</v>
+      </c>
+      <c r="F15">
+        <v>0.61016949152542299</v>
+      </c>
+      <c r="G15">
+        <v>0.56949152542372805</v>
+      </c>
+      <c r="H15">
+        <v>0.57627118644067798</v>
+      </c>
+      <c r="I15">
+        <v>0.62711864406779605</v>
+      </c>
+      <c r="J15">
+        <v>0.48426150121065298</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" si="0"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>1</v>
@@ -1394,7 +1389,7 @@
       </c>
       <c r="P15" s="1">
         <f>_xlfn.T.TEST(D8:J8,D14:J14,2,1)</f>
-        <v>7.5800615073385445E-6</v>
+        <v>4.5327001486166717E-7</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -1407,11 +1402,11 @@
       </c>
       <c r="U15" s="2">
         <f t="shared" si="1"/>
-        <v>0.68281748956030441</v>
+        <v>0.58934624697336491</v>
       </c>
       <c r="V15" s="2">
         <f t="shared" si="2"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
@@ -1424,30 +1419,30 @@
       <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="2">
-        <v>0.91959776149664296</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.92209296604033397</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.91623335091505897</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.93066775677763303</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.92106950699227497</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0.92028866738132797</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0.91974749987155802</v>
+      <c r="D16">
+        <v>0.94005847953216304</v>
+      </c>
+      <c r="E16">
+        <v>0.92925451488518296</v>
+      </c>
+      <c r="F16">
+        <v>0.93863600442547801</v>
+      </c>
+      <c r="G16">
+        <v>0.93472912183438395</v>
+      </c>
+      <c r="H16">
+        <v>0.92570436218789398</v>
+      </c>
+      <c r="I16">
+        <v>0.93798386982767101</v>
+      </c>
+      <c r="J16">
+        <v>0.94163512635751501</v>
       </c>
       <c r="K16" s="2">
         <f t="shared" si="0"/>
-        <v>0.93066775677763303</v>
+        <v>0.94163512635751501</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" t="s">
@@ -1455,7 +1450,7 @@
       </c>
       <c r="P16" s="1">
         <f>_xlfn.T.TEST(D9:J9,D15:J15,2,1)</f>
-        <v>3.3522300830370901E-4</v>
+        <v>5.890123830280726E-2</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -1468,11 +1463,11 @@
       </c>
       <c r="U16" s="2">
         <f t="shared" si="1"/>
-        <v>0.92254565828155799</v>
+        <v>0.93620457567597548</v>
       </c>
       <c r="V16" s="2">
         <f t="shared" si="2"/>
-        <v>0.93066775677763303</v>
+        <v>0.94163512635751501</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
@@ -1482,7 +1477,7 @@
       </c>
       <c r="P17" s="1">
         <f>_xlfn.T.TEST(D10:J10,D16:J16,2,1)</f>
-        <v>4.0113062626699511E-4</v>
+        <v>2.4052791298279506E-2</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
@@ -1593,12 +1588,12 @@
       </c>
       <c r="E20">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
       <c r="G20">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -1609,7 +1604,7 @@
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <f t="shared" si="3"/>
@@ -1626,34 +1621,34 @@
       </c>
       <c r="Q20" s="2">
         <f t="shared" ref="Q20:Q33" si="4">E3</f>
-        <v>0.31481481481481399</v>
+        <v>0.38585858585858501</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" ref="R20:R33" si="5">G3</f>
-        <v>0.53939716999418497</v>
+        <v>0.62009803921568596</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" ref="S20:S33" si="6">H3</f>
-        <v>0.61033411033411</v>
+        <v>0.664251207729468</v>
       </c>
       <c r="T20">
         <v>0.70630000000000004</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" ref="U20:U33" si="7">I3</f>
-        <v>0.40201465201465197</v>
+        <v>0.60101010101010099</v>
       </c>
       <c r="V20" s="2">
         <f t="shared" ref="V20:V33" si="8">F3</f>
-        <v>0.44775132275132201</v>
+        <v>0.379212204007286</v>
       </c>
       <c r="W20" s="2">
         <f t="shared" ref="W20:W33" si="9">D3</f>
-        <v>0.25164835164835098</v>
+        <v>0.25484351713859899</v>
       </c>
       <c r="X20" s="1">
         <f>_xlfn.T.TEST(Q20:U20,V20:W20,2,3)</f>
-        <v>0.29710206253622506</v>
+        <v>4.9461999634786438E-2</v>
       </c>
       <c r="Z20" t="s">
         <v>3</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AC20" s="1">
         <f>X20</f>
-        <v>0.29710206253622506</v>
+        <v>4.9461999634786438E-2</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
@@ -1681,23 +1676,23 @@
       </c>
       <c r="D21">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="E21">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F21">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G21">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="H21">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
@@ -1705,7 +1700,7 @@
       </c>
       <c r="J21">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="N21" t="s">
         <v>3</v>
@@ -1722,37 +1717,37 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
-        <v>0.88753387533875305</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="6"/>
-        <v>0.88753387533875305</v>
+        <v>0.88888888888888795</v>
       </c>
       <c r="T21">
         <v>1.7062999999999999</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="7"/>
-        <v>0.64176706827309205</v>
+        <v>0.65079365079365004</v>
       </c>
       <c r="V21" s="2">
         <f t="shared" si="8"/>
-        <v>0.88753387533875305</v>
+        <v>0.88888888888888795</v>
       </c>
       <c r="W21" s="2">
         <f t="shared" si="9"/>
-        <v>0.85049683830171596</v>
+        <v>0.88888888888888795</v>
       </c>
       <c r="X21" s="1">
         <f t="shared" ref="X21:X33" si="10">_xlfn.T.TEST(Q21:U21,V21:W21,2,3)</f>
-        <v>0.50625183666725238</v>
+        <v>0.57780204465388896</v>
       </c>
       <c r="AB21" t="s">
         <v>6</v>
       </c>
       <c r="AC21" s="1">
         <f>X21</f>
-        <v>0.50625183666725238</v>
+        <v>0.57780204465388896</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
@@ -1767,31 +1762,31 @@
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <f t="shared" si="3"/>
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <f t="shared" si="3"/>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N22" t="s">
         <v>3</v>
@@ -1804,41 +1799,41 @@
       </c>
       <c r="Q22" s="2">
         <f t="shared" si="4"/>
-        <v>0.56451612903225801</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
-        <v>0.532258064516129</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="S22" s="2">
         <f t="shared" si="6"/>
-        <v>0.54838709677419295</v>
+        <v>0.60628618693134795</v>
       </c>
       <c r="T22">
         <v>2.7063000000000001</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" si="7"/>
-        <v>0.56451612903225801</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="V22" s="2">
         <f t="shared" si="8"/>
-        <v>0.54838709677419295</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="W22" s="2">
         <f t="shared" si="9"/>
-        <v>0.54838709677419295</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="X22" s="1">
         <f t="shared" si="10"/>
-        <v>0.36994244699650658</v>
+        <v>0.37949638860772705</v>
       </c>
       <c r="AB22" t="s">
         <v>7</v>
       </c>
       <c r="AC22" s="1">
         <f t="shared" ref="AC22:AC33" si="11">X22</f>
-        <v>0.36994244699650658</v>
+        <v>0.37949638860772705</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
@@ -1853,31 +1848,31 @@
       </c>
       <c r="D23">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="F23">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
       <c r="I23">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="J23">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23" t="s">
         <v>3</v>
@@ -1890,41 +1885,41 @@
       </c>
       <c r="Q23" s="2">
         <f t="shared" si="4"/>
-        <v>0.93693624809750697</v>
+        <v>0.97951929748316902</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
-        <v>0.93921254899805395</v>
+        <v>0.99079733231383504</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="6"/>
-        <v>0.94103105767865403</v>
+        <v>0.97886931772310704</v>
       </c>
       <c r="T23">
         <v>3.7063000000000001</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="7"/>
-        <v>0.93818995798279103</v>
+        <v>0.98281862412784504</v>
       </c>
       <c r="V23" s="2">
         <f t="shared" si="8"/>
-        <v>0.937398235085805</v>
+        <v>0.99155089836204302</v>
       </c>
       <c r="W23" s="2">
         <f t="shared" si="9"/>
-        <v>0.93268535020237997</v>
+        <v>0.93669025088477198</v>
       </c>
       <c r="X23" s="1">
         <f t="shared" si="10"/>
-        <v>0.3709653179121149</v>
+        <v>0.35954893418574324</v>
       </c>
       <c r="AB23" t="s">
         <v>8</v>
       </c>
       <c r="AC23" s="1">
         <f t="shared" si="11"/>
-        <v>0.3709653179121149</v>
+        <v>0.35954893418574324</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
@@ -1943,15 +1938,15 @@
       </c>
       <c r="E24">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <f t="shared" si="3"/>
@@ -1976,34 +1971,34 @@
       </c>
       <c r="Q24" s="2">
         <f t="shared" si="4"/>
-        <v>0.51165501165501104</v>
+        <v>0.54836182336182304</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
-        <v>0.43153594771241799</v>
+        <v>0.62009803921568596</v>
       </c>
       <c r="S24" s="2">
         <f t="shared" si="6"/>
-        <v>0.391666666666666</v>
+        <v>0.39951134930643101</v>
       </c>
       <c r="T24">
         <v>4.7062999999999997</v>
       </c>
       <c r="U24" s="2">
         <f t="shared" si="7"/>
-        <v>0.45571658615136801</v>
+        <v>0.47202380952380901</v>
       </c>
       <c r="V24" s="2">
         <f t="shared" si="8"/>
-        <v>0.48756218905472598</v>
+        <v>0.45320512820512798</v>
       </c>
       <c r="W24" s="2">
         <f t="shared" si="9"/>
-        <v>0.416901408450704</v>
+        <v>0.43497474747474701</v>
       </c>
       <c r="X24" s="1">
         <f t="shared" si="10"/>
-        <v>0.37652169714308786</v>
+        <v>0.34191885304663833</v>
       </c>
       <c r="AA24" t="s">
         <v>9</v>
@@ -2013,7 +2008,7 @@
       </c>
       <c r="AC24" s="1">
         <f t="shared" si="11"/>
-        <v>0.37652169714308786</v>
+        <v>0.34191885304663833</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
@@ -2028,31 +2023,31 @@
       </c>
       <c r="D25">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E25">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F25">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G25">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I25">
         <f>_xlfn.RANK.AVG(I8, $D8:$J8, 0)</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J25">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="s">
         <v>3</v>
@@ -2065,15 +2060,15 @@
       </c>
       <c r="Q25" s="2">
         <f t="shared" si="4"/>
-        <v>0.88753387533875305</v>
+        <v>0.88888888888888795</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
-        <v>0.88753387533875305</v>
+        <v>0.88723051409618503</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="6"/>
-        <v>0.88753387533875305</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="T25">
         <v>5.7062999999999997</v>
@@ -2084,22 +2079,22 @@
       </c>
       <c r="V25" s="2">
         <f t="shared" si="8"/>
-        <v>0.85049683830171596</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="W25" s="2">
         <f t="shared" si="9"/>
-        <v>0.88753387533875305</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="X25" s="1">
         <f t="shared" si="10"/>
-        <v>0.36562170119170334</v>
+        <v>0.36491857582175741</v>
       </c>
       <c r="AB25" t="s">
         <v>6</v>
       </c>
       <c r="AC25" s="1">
         <f t="shared" si="11"/>
-        <v>0.36562170119170334</v>
+        <v>0.36491857582175741</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
@@ -2114,27 +2109,27 @@
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="E26">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="F26">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
       <c r="G26">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J26">
         <f t="shared" si="3"/>
@@ -2151,41 +2146,41 @@
       </c>
       <c r="Q26" s="2">
         <f t="shared" si="4"/>
-        <v>0.56451612903225801</v>
+        <v>0.61972704714640103</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
-        <v>0.54838709677419295</v>
+        <v>0.611662531017369</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="6"/>
-        <v>0.54838709677419295</v>
+        <v>0.59553349875930495</v>
       </c>
       <c r="T26">
         <v>6.7062999999999997</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="7"/>
-        <v>0.56451612903225801</v>
+        <v>0.62375930521091805</v>
       </c>
       <c r="V26" s="2">
         <f t="shared" si="8"/>
-        <v>0.54838709677419295</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="W26" s="2">
         <f t="shared" si="9"/>
-        <v>0.54838709677419295</v>
+        <v>0.62779156327543395</v>
       </c>
       <c r="X26" s="1">
         <f t="shared" si="10"/>
-        <v>0.37109708565412991</v>
+        <v>0.37926416149327408</v>
       </c>
       <c r="AB26" t="s">
         <v>7</v>
       </c>
       <c r="AC26" s="1">
         <f t="shared" si="11"/>
-        <v>0.37109708565412991</v>
+        <v>0.37926416149327408</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
@@ -2204,7 +2199,7 @@
       </c>
       <c r="E27">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <f t="shared" si="3"/>
@@ -2212,7 +2207,7 @@
       </c>
       <c r="G27">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <f t="shared" si="3"/>
@@ -2220,11 +2215,11 @@
       </c>
       <c r="I27">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J27">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N27" t="s">
         <v>3</v>
@@ -2237,41 +2232,41 @@
       </c>
       <c r="Q27" s="2">
         <f t="shared" si="4"/>
-        <v>0.93764496357021698</v>
+        <v>0.94266032312419401</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
-        <v>0.936997318893808</v>
+        <v>0.98835886192977496</v>
       </c>
       <c r="S27" s="2">
         <f t="shared" si="6"/>
-        <v>0.93419117816160502</v>
+        <v>0.93328442743446405</v>
       </c>
       <c r="T27">
         <v>7.7062999999999997</v>
       </c>
       <c r="U27" s="2">
         <f t="shared" si="7"/>
-        <v>0.93158403611311402</v>
+        <v>0.98655523612953899</v>
       </c>
       <c r="V27" s="2">
         <f t="shared" si="8"/>
-        <v>0.93944455915457203</v>
+        <v>0.98886359468137797</v>
       </c>
       <c r="W27" s="2">
         <f t="shared" si="9"/>
-        <v>0.93973917514745398</v>
+        <v>0.99481979448093305</v>
       </c>
       <c r="X27" s="1">
         <f t="shared" si="10"/>
-        <v>0.37532610068127725</v>
+        <v>0.38328835155067859</v>
       </c>
       <c r="AB27" t="s">
         <v>8</v>
       </c>
       <c r="AC27" s="1">
         <f t="shared" si="11"/>
-        <v>0.37532610068127725</v>
+        <v>0.38328835155067859</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
@@ -2286,27 +2281,27 @@
       </c>
       <c r="D28">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J28">
         <f t="shared" si="3"/>
@@ -2327,7 +2322,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
-        <v>0.98611111111111105</v>
+        <v>1</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="6"/>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="U28" s="2">
         <f t="shared" si="7"/>
-        <v>0.99572649572649496</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2">
         <f t="shared" si="8"/>
@@ -2346,11 +2341,11 @@
       </c>
       <c r="W28" s="2">
         <f t="shared" si="9"/>
-        <v>0.99572649572649496</v>
+        <v>0.99862825788751697</v>
       </c>
       <c r="X28" s="1">
         <f t="shared" si="10"/>
-        <v>0.37457148721099831</v>
+        <v>0.37370997793474503</v>
       </c>
       <c r="Z28" t="s">
         <v>10</v>
@@ -2363,7 +2358,7 @@
       </c>
       <c r="AC28" s="1">
         <f t="shared" si="11"/>
-        <v>0.37457148721099831</v>
+        <v>0.37370997793474503</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
@@ -2378,11 +2373,11 @@
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F29">
         <f t="shared" si="3"/>
@@ -2398,7 +2393,7 @@
       </c>
       <c r="I29">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J29">
         <f t="shared" si="3"/>
@@ -2415,41 +2410,41 @@
       </c>
       <c r="Q29" s="2">
         <f t="shared" si="4"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
-        <v>0.677966101694915</v>
+        <v>0.57627118644067798</v>
       </c>
       <c r="S29" s="2">
         <f t="shared" si="6"/>
-        <v>0.677966101694915</v>
+        <v>0.57627118644067798</v>
       </c>
       <c r="T29">
         <v>9.7063000000000006</v>
       </c>
       <c r="U29" s="2">
         <f t="shared" si="7"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="V29" s="2">
         <f t="shared" si="8"/>
-        <v>0.68926553672316304</v>
+        <v>0.59322033898305004</v>
       </c>
       <c r="W29" s="2">
         <f t="shared" si="9"/>
-        <v>0.71186440677966101</v>
+        <v>0.61016949152542299</v>
       </c>
       <c r="X29" s="1">
         <f t="shared" si="10"/>
-        <v>0.37525702085671403</v>
+        <v>0.37391170543636998</v>
       </c>
       <c r="AB29" t="s">
         <v>7</v>
       </c>
       <c r="AC29" s="1">
         <f t="shared" si="11"/>
-        <v>0.37525702085671403</v>
+        <v>0.37391170543636998</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
@@ -2464,31 +2459,31 @@
       </c>
       <c r="D30">
         <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E30">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
       <c r="I30">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="s">
         <v>10</v>
@@ -2501,41 +2496,41 @@
       </c>
       <c r="Q30" s="2">
         <f t="shared" si="4"/>
-        <v>0.93055030097717195</v>
+        <v>0.93463006505356605</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
-        <v>0.90245218913699399</v>
+        <v>0.941720406904897</v>
       </c>
       <c r="S30" s="2">
         <f t="shared" si="6"/>
-        <v>0.92046569313716597</v>
+        <v>0.93263625000406802</v>
       </c>
       <c r="T30">
         <v>10.706300000000001</v>
       </c>
       <c r="U30" s="2">
         <f t="shared" si="7"/>
-        <v>0.91508525064456303</v>
+        <v>0.93774124646253598</v>
       </c>
       <c r="V30" s="2">
         <f t="shared" si="8"/>
-        <v>0.91151442820615702</v>
+        <v>0.93031331017644503</v>
       </c>
       <c r="W30" s="2">
         <f t="shared" si="9"/>
-        <v>0.91333063316442797</v>
+        <v>0.93239539171778496</v>
       </c>
       <c r="X30" s="1">
         <f t="shared" si="10"/>
-        <v>0.37286927063437891</v>
+        <v>0.37273211125587602</v>
       </c>
       <c r="AB30" t="s">
         <v>8</v>
       </c>
       <c r="AC30" s="1">
         <f t="shared" si="11"/>
-        <v>0.37286927063437891</v>
+        <v>0.37273211125587602</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
@@ -2550,31 +2545,31 @@
       </c>
       <c r="D31">
         <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="E31">
-        <f t="shared" si="3"/>
-        <v>1.5</v>
-      </c>
       <c r="F31">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="G31">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <f t="shared" si="3"/>
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N31" t="s">
         <v>10</v>
@@ -2587,34 +2582,34 @@
       </c>
       <c r="Q31" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.99862825788751697</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
-        <v>0.99711399711399695</v>
+        <v>1</v>
       </c>
       <c r="S31" s="2">
         <f t="shared" si="6"/>
-        <v>0.98611111111111105</v>
+        <v>1</v>
       </c>
       <c r="T31">
         <v>11.706300000000001</v>
       </c>
       <c r="U31" s="2">
         <f t="shared" si="7"/>
-        <v>0.97855750487329396</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.99862825788751697</v>
       </c>
       <c r="W31" s="2">
         <f t="shared" si="9"/>
-        <v>0.97855750487329396</v>
+        <v>1</v>
       </c>
       <c r="X31" s="1">
         <f t="shared" si="10"/>
-        <v>0.37367070209701275</v>
+        <v>0.3738322295744923</v>
       </c>
       <c r="AA31" t="s">
         <v>9</v>
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AC31" s="1">
         <f t="shared" si="11"/>
-        <v>0.37367070209701275</v>
+        <v>0.3738322295744923</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
@@ -2639,27 +2634,27 @@
       </c>
       <c r="D32">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F32">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J32">
         <f t="shared" si="3"/>
@@ -2676,41 +2671,41 @@
       </c>
       <c r="Q32" s="2">
         <f t="shared" si="4"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
-        <v>0.69491525423728795</v>
+        <v>0.56949152542372805</v>
       </c>
       <c r="S32" s="2">
         <f t="shared" si="6"/>
-        <v>0.69491525423728795</v>
+        <v>0.57627118644067798</v>
       </c>
       <c r="T32">
         <v>12.706300000000001</v>
       </c>
       <c r="U32" s="2">
         <f t="shared" si="7"/>
-        <v>0.71186440677966101</v>
+        <v>0.62711864406779605</v>
       </c>
       <c r="V32" s="2">
         <f t="shared" si="8"/>
-        <v>0.68852861704740798</v>
+        <v>0.61016949152542299</v>
       </c>
       <c r="W32" s="2">
         <f t="shared" si="9"/>
-        <v>0.71186440677966101</v>
+        <v>0.59322033898305004</v>
       </c>
       <c r="X32" s="1">
         <f t="shared" si="10"/>
-        <v>0.37333336345176932</v>
+        <v>0.37420837393187562</v>
       </c>
       <c r="AB32" t="s">
         <v>7</v>
       </c>
       <c r="AC32" s="1">
         <f t="shared" si="11"/>
-        <v>0.37333336345176932</v>
+        <v>0.37420837393187562</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
@@ -2725,23 +2720,23 @@
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
@@ -2749,7 +2744,7 @@
       </c>
       <c r="J33">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N33" t="s">
         <v>10</v>
@@ -2762,41 +2757,41 @@
       </c>
       <c r="Q33" s="2">
         <f t="shared" si="4"/>
-        <v>0.92209296604033397</v>
+        <v>0.92925451488518296</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
-        <v>0.93066775677763303</v>
+        <v>0.93472912183438395</v>
       </c>
       <c r="S33" s="2">
         <f t="shared" si="6"/>
-        <v>0.92106950699227497</v>
+        <v>0.92570436218789398</v>
       </c>
       <c r="T33">
         <v>13.706300000000001</v>
       </c>
       <c r="U33" s="2">
         <f t="shared" si="7"/>
-        <v>0.92028866738132797</v>
+        <v>0.93798386982767101</v>
       </c>
       <c r="V33" s="2">
         <f t="shared" si="8"/>
-        <v>0.91623335091505897</v>
+        <v>0.93863600442547801</v>
       </c>
       <c r="W33" s="2">
         <f t="shared" si="9"/>
-        <v>0.91959776149664296</v>
+        <v>0.94005847953216304</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" si="10"/>
-        <v>0.37295936902999283</v>
+        <v>0.37515136515070147</v>
       </c>
       <c r="AB33" t="s">
         <v>8</v>
       </c>
       <c r="AC33" s="1">
         <f t="shared" si="11"/>
-        <v>0.37295936902999283</v>
+        <v>0.37515136515070147</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
@@ -2805,31 +2800,31 @@
       </c>
       <c r="D34">
         <f>AVERAGE(D20:D33)</f>
-        <v>4.5714285714285712</v>
+        <v>3.9642857142857144</v>
       </c>
       <c r="E34">
         <f t="shared" ref="E34:J34" si="12">AVERAGE(E20:E33)</f>
-        <v>2.3928571428571428</v>
+        <v>3.4642857142857144</v>
       </c>
       <c r="F34">
         <f t="shared" si="12"/>
-        <v>4.0714285714285712</v>
+        <v>3.6428571428571428</v>
       </c>
       <c r="G34">
         <f t="shared" si="12"/>
-        <v>4.2142857142857144</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="H34">
         <f t="shared" si="12"/>
-        <v>3.8571428571428572</v>
+        <v>4.8214285714285712</v>
       </c>
       <c r="I34">
         <f t="shared" si="12"/>
-        <v>3.6428571428571428</v>
+        <v>3.0357142857142856</v>
       </c>
       <c r="J34">
         <f t="shared" si="12"/>
-        <v>5.25</v>
+        <v>5.6428571428571432</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
@@ -2838,11 +2833,11 @@
       </c>
       <c r="D35">
         <f t="shared" ref="D35:J35" si="13">_xlfn.RANK.AVG(D34, $D34:$J34, 1)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <f t="shared" si="13"/>
@@ -2850,15 +2845,15 @@
       </c>
       <c r="G35">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <f t="shared" si="13"/>
